--- a/seun-두경부암/정박사님께 드릴 raw data.xlsx
+++ b/seun-두경부암/정박사님께 드릴 raw data.xlsx
@@ -15727,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="BM53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BN53" s="1">
         <v>4</v>
